--- a/rules/merge/kinds/fund_structure.xlsx
+++ b/rules/merge/kinds/fund_structure.xlsx
@@ -774,7 +774,7 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>The record's SEC_SERIES_ID is the one a Company holds; and Exactly one Company holds that SEC_SERIES_ID, or none</t>
+          <t>The record's SEC_SERIES_ID is the one a Fund structure holds; and Exactly one Fund structure holds that SEC_SERIES_ID, or none</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>The record's LEI is the one a Company holds; and Exactly one Company holds that LEI, or none</t>
+          <t>The record's LEI is the one a Fund structure holds; and Exactly one Fund structure holds that LEI, or none</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
           <t>rules file comment</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/rules/merge/kinds/fund_structure.xlsx
+++ b/rules/merge/kinds/fund_structure.xlsx
@@ -478,7 +478,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>fund_structure-2026-10-15.1</t>
+          <t>fund_structure-2026-10-25.one-value-per-identifier</t>
         </is>
       </c>
     </row>
